--- a/nfl.xlsx
+++ b/nfl.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafay\Documents\GitHub\HigherLower0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78A16BCE-92A5-4CE2-932B-F30A7533E026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4593C7-3297-4044-B940-3978F2540059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{EDEEB438-CE4F-4046-B620-1EAF5CB4362B}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1935" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{EDEEB438-CE4F-4046-B620-1EAF5CB4362B}"/>
   </bookViews>
   <sheets>
     <sheet name="mvp" sheetId="7" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">def!$A$1:$C$55</definedName>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">defrook!$A$1:$C$59</definedName>
+    <definedName name="ExternalData_1" localSheetId="4" hidden="1">defrook!$A$1:$C$60</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">off!$A$1:$B$54</definedName>
     <definedName name="ExternalData_1" localSheetId="3" hidden="1">offrook!$A$1:$D$59</definedName>
     <definedName name="ExternalData_1" localSheetId="6" hidden="1">smvp!$A$1:$F$61</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="771">
   <si>
     <t>Year</t>
   </si>
@@ -847,9 +847,6 @@
     <t>Jim Haslett</t>
   </si>
   <si>
-    <t>Buddy CurryAl Richardson</t>
-  </si>
-  <si>
     <t>Chip Banks</t>
   </si>
   <si>
@@ -2381,6 +2378,12 @@
   </si>
   <si>
     <t>Tyron Smith</t>
+  </si>
+  <si>
+    <t>Buddy Curry</t>
+  </si>
+  <si>
+    <t>Al Richardson</t>
   </si>
 </sst>
 </file>
@@ -2599,8 +2602,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{55192B8C-B8D8-4C9B-9030-AD6D663564EC}" name="Table_3" displayName="Table_3" ref="A1:C59" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C59" xr:uid="{55192B8C-B8D8-4C9B-9030-AD6D663564EC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{55192B8C-B8D8-4C9B-9030-AD6D663564EC}" name="Table_3" displayName="Table_3" ref="A1:C60" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C60" xr:uid="{55192B8C-B8D8-4C9B-9030-AD6D663564EC}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5F817472-2D1E-4CA0-8636-66D8F01C9CAA}" uniqueName="1" name="Season" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{DC718BE1-3E95-419C-8DE6-DB0A4420FA5F}" uniqueName="2" name="Player" queryTableFieldId="2" dataDxfId="6"/>
@@ -5673,7 +5676,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D729FD-8BCC-4774-B8DC-08FAAE177E0E}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -5840,7 +5843,7 @@
         <v>1980</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>258</v>
+        <v>770</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>112</v>
@@ -5848,10 +5851,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>769</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>112</v>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>259</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>112</v>
@@ -5870,10 +5873,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>112</v>
@@ -5881,120 +5884,120 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>144</v>
+        <v>268</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>270</v>
+        <v>144</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>102</v>
@@ -6002,21 +6005,21 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>115</v>
@@ -6024,54 +6027,54 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>112</v>
@@ -6079,32 +6082,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>112</v>
@@ -6112,10 +6115,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>112</v>
@@ -6123,10 +6126,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>112</v>
@@ -6134,10 +6137,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>112</v>
@@ -6145,10 +6148,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>112</v>
@@ -6156,10 +6159,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>112</v>
@@ -6167,32 +6170,32 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>112</v>
@@ -6200,87 +6203,87 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>287</v>
+        <v>164</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>288</v>
+        <v>169</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>115</v>
@@ -6288,46 +6291,57 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
+        <v>2023</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
         <v>2024</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -6363,10 +6377,10 @@
         <v>1963</v>
       </c>
       <c r="B2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
         <v>298</v>
-      </c>
-      <c r="C2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6374,7 +6388,7 @@
         <v>1963</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
         <v>183</v>
@@ -6397,7 +6411,7 @@
         <v>1964</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -6420,7 +6434,7 @@
         <v>1965</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C7" t="s">
         <v>183</v>
@@ -6431,7 +6445,7 @@
         <v>1966</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C8" t="str">
         <f>C7</f>
@@ -6443,7 +6457,7 @@
         <v>1966</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
         <v>188</v>
@@ -6454,7 +6468,7 @@
         <v>1998</v>
       </c>
       <c r="B10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
         <v>188</v>
@@ -6465,7 +6479,7 @@
         <v>1999</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
         <v>102</v>
@@ -6476,7 +6490,7 @@
         <v>2000</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
@@ -6487,7 +6501,7 @@
         <v>2001</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C13" t="s">
         <v>183</v>
@@ -6498,7 +6512,7 @@
         <v>2002</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C14" t="s">
         <v>188</v>
@@ -6509,7 +6523,7 @@
         <v>2003</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" ref="C15:C16" si="1">C14</f>
@@ -6533,7 +6547,7 @@
         <v>2005</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C17" t="s">
         <v>112</v>
@@ -6544,7 +6558,7 @@
         <v>2005</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C18" t="s">
         <v>185</v>
@@ -6555,7 +6569,7 @@
         <v>2006</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C19" t="s">
         <v>188</v>
@@ -6566,7 +6580,7 @@
         <v>2007</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C20" t="s">
         <v>115</v>
@@ -6577,7 +6591,7 @@
         <v>2008</v>
       </c>
       <c r="B21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
         <v>188</v>
@@ -6600,7 +6614,7 @@
         <v>2010</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="2"/>
@@ -6612,7 +6626,7 @@
         <v>2011</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="2"/>
@@ -6636,7 +6650,7 @@
         <v>2013</v>
       </c>
       <c r="B26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="2"/>
@@ -6648,10 +6662,10 @@
         <v>2014</v>
       </c>
       <c r="B27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" t="s">
         <v>319</v>
-      </c>
-      <c r="C27" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6659,7 +6673,7 @@
         <v>2015</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C28" t="s">
         <v>107</v>
@@ -6670,7 +6684,7 @@
         <v>2016</v>
       </c>
       <c r="B29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C29" t="s">
         <v>185</v>
@@ -6681,7 +6695,7 @@
         <v>2017</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C30" t="str">
         <f>C29</f>
@@ -6693,7 +6707,7 @@
         <v>2018</v>
       </c>
       <c r="B31" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C31" t="s">
         <v>188</v>
@@ -6704,7 +6718,7 @@
         <v>2019</v>
       </c>
       <c r="B32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" ref="C32:C38" si="3">C31</f>
@@ -6716,7 +6730,7 @@
         <v>2020</v>
       </c>
       <c r="B33" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="3"/>
@@ -6728,7 +6742,7 @@
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="3"/>
@@ -6740,7 +6754,7 @@
         <v>2022</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="3"/>
@@ -6752,7 +6766,7 @@
         <v>2023</v>
       </c>
       <c r="B36" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="3"/>
@@ -6764,7 +6778,7 @@
         <v>2024</v>
       </c>
       <c r="B37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="3"/>
@@ -6791,13 +6805,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" t="s">
         <v>331</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>332</v>
-      </c>
-      <c r="C1" t="s">
-        <v>333</v>
       </c>
       <c r="D1" t="s">
         <v>180</v>
@@ -6806,7 +6820,7 @@
         <v>100</v>
       </c>
       <c r="F1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75">
@@ -6814,10 +6828,10 @@
         <v>1967</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>146</v>
@@ -6826,7 +6840,7 @@
         <v>188</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H2" s="2"/>
     </row>
@@ -6835,19 +6849,19 @@
         <v>1968</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6855,19 +6869,19 @@
         <v>1969</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6875,19 +6889,19 @@
         <v>1970</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>246</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6895,10 +6909,10 @@
         <v>1971</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>114</v>
@@ -6907,7 +6921,7 @@
         <v>112</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6915,19 +6929,19 @@
         <v>1972</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6935,10 +6949,10 @@
         <v>1973</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>106</v>
@@ -6947,7 +6961,7 @@
         <v>107</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6955,19 +6969,19 @@
         <v>1974</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6975,19 +6989,19 @@
         <v>1975</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -6995,19 +7009,19 @@
         <v>1976</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>185</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -7015,19 +7029,19 @@
         <v>1977</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7035,19 +7049,19 @@
         <v>1978</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7055,19 +7069,19 @@
         <v>1978</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -7075,19 +7089,19 @@
         <v>1979</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -7095,19 +7109,19 @@
         <v>1980</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7115,19 +7129,19 @@
         <v>1981</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7135,19 +7149,19 @@
         <v>1982</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7155,19 +7169,19 @@
         <v>1983</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>195</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7175,19 +7189,19 @@
         <v>1984</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7195,19 +7209,19 @@
         <v>1985</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7215,19 +7229,19 @@
         <v>1986</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7235,7 +7249,7 @@
         <v>1987</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>39</v>
@@ -7244,10 +7258,10 @@
         <v>122</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7255,19 +7269,19 @@
         <v>1988</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7275,19 +7289,19 @@
         <v>1989</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7295,19 +7309,19 @@
         <v>1990</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7315,19 +7329,19 @@
         <v>1991</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7335,19 +7349,19 @@
         <v>1992</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7355,19 +7369,19 @@
         <v>1993</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7375,19 +7389,19 @@
         <v>1994</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7395,19 +7409,19 @@
         <v>1995</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -7415,19 +7429,19 @@
         <v>1996</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -7435,19 +7449,19 @@
         <v>1997</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -7455,19 +7469,19 @@
         <v>1998</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -7475,19 +7489,19 @@
         <v>1999</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -7495,19 +7509,19 @@
         <v>2000</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>230</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -7515,19 +7529,19 @@
         <v>2001</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -7535,19 +7549,19 @@
         <v>2002</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>173</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -7555,19 +7569,19 @@
         <v>2003</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -7575,19 +7589,19 @@
         <v>2004</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -7595,19 +7609,19 @@
         <v>2005</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -7615,19 +7629,19 @@
         <v>2006</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="F42" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -7635,19 +7649,19 @@
         <v>2007</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>157</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -7655,19 +7669,19 @@
         <v>2008</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -7675,19 +7689,19 @@
         <v>2009</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -7695,19 +7709,19 @@
         <v>2010</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -7715,19 +7729,19 @@
         <v>2011</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -7735,19 +7749,19 @@
         <v>2012</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -7755,19 +7769,19 @@
         <v>2013</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -7775,19 +7789,19 @@
         <v>2014</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>126</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -7795,19 +7809,19 @@
         <v>2015</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -7815,19 +7829,19 @@
         <v>2016</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -7835,19 +7849,19 @@
         <v>2017</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -7855,19 +7869,19 @@
         <v>2018</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>131</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -7875,19 +7889,19 @@
         <v>2019</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -7895,19 +7909,19 @@
         <v>2020</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -7915,19 +7929,19 @@
         <v>2021</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -7935,19 +7949,19 @@
         <v>2022</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -7955,19 +7969,19 @@
         <v>2023</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -7975,19 +7989,19 @@
         <v>2024</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -7995,19 +8009,19 @@
         <v>2025</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -8032,10 +8046,10 @@
         <v>179</v>
       </c>
       <c r="B1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C1" t="s">
         <v>581</v>
-      </c>
-      <c r="C1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75">
@@ -8043,7 +8057,7 @@
         <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C2">
         <v>13</v>
@@ -8052,10 +8066,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B3" t="s">
         <v>584</v>
-      </c>
-      <c r="B3" t="s">
-        <v>585</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -8066,7 +8080,7 @@
         <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -8077,7 +8091,7 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -8085,10 +8099,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B6" t="s">
         <v>587</v>
-      </c>
-      <c r="B6" t="s">
-        <v>588</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -8099,7 +8113,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -8110,7 +8124,7 @@
         <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -8121,7 +8135,7 @@
         <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -8129,10 +8143,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B10" t="s">
         <v>591</v>
-      </c>
-      <c r="B10" t="s">
-        <v>592</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -8140,10 +8154,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -8151,10 +8165,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" t="s">
         <v>594</v>
-      </c>
-      <c r="B12" t="s">
-        <v>595</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -8165,7 +8179,7 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -8173,10 +8187,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B14" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -8184,10 +8198,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -8195,10 +8209,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>598</v>
+      </c>
+      <c r="B16" t="s">
         <v>599</v>
-      </c>
-      <c r="B16" t="s">
-        <v>600</v>
       </c>
       <c r="C16">
         <v>9</v>
@@ -8206,10 +8220,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C17">
         <v>9</v>
@@ -8220,7 +8234,7 @@
         <v>151</v>
       </c>
       <c r="B18" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -8228,10 +8242,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>601</v>
+      </c>
+      <c r="B19" t="s">
         <v>602</v>
-      </c>
-      <c r="B19" t="s">
-        <v>603</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -8239,10 +8253,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>603</v>
+      </c>
+      <c r="B20" t="s">
         <v>604</v>
-      </c>
-      <c r="B20" t="s">
-        <v>605</v>
       </c>
       <c r="C20">
         <v>9</v>
@@ -8250,10 +8264,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>605</v>
+      </c>
+      <c r="B21" t="s">
         <v>606</v>
-      </c>
-      <c r="B21" t="s">
-        <v>607</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -8261,10 +8275,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -8272,10 +8286,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>608</v>
+      </c>
+      <c r="B23" t="s">
         <v>609</v>
-      </c>
-      <c r="B23" t="s">
-        <v>610</v>
       </c>
       <c r="C23">
         <v>9</v>
@@ -8286,7 +8300,7 @@
         <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C24">
         <v>9</v>
@@ -8294,10 +8308,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B25" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C25">
         <v>9</v>
@@ -8305,10 +8319,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C26">
         <v>9</v>
@@ -8316,10 +8330,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B27" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C27">
         <v>9</v>
@@ -8327,10 +8341,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>614</v>
+      </c>
+      <c r="B28" t="s">
         <v>615</v>
-      </c>
-      <c r="B28" t="s">
-        <v>616</v>
       </c>
       <c r="C28">
         <v>8</v>
@@ -8338,10 +8352,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>616</v>
+      </c>
+      <c r="B29" t="s">
         <v>617</v>
-      </c>
-      <c r="B29" t="s">
-        <v>618</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -8349,10 +8363,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>618</v>
+      </c>
+      <c r="B30" t="s">
         <v>619</v>
-      </c>
-      <c r="B30" t="s">
-        <v>620</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -8363,7 +8377,7 @@
         <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -8371,10 +8385,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>620</v>
+      </c>
+      <c r="B32" t="s">
         <v>621</v>
-      </c>
-      <c r="B32" t="s">
-        <v>622</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -8382,10 +8396,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -8393,10 +8407,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B34" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C34">
         <v>8</v>
@@ -8404,10 +8418,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B35" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -8418,7 +8432,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C36">
         <v>8</v>
@@ -8429,7 +8443,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C37">
         <v>8</v>
@@ -8437,10 +8451,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B38" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C38">
         <v>8</v>
@@ -8451,7 +8465,7 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C39">
         <v>8</v>
@@ -8459,10 +8473,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B40" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C40">
         <v>8</v>
@@ -8473,7 +8487,7 @@
         <v>127</v>
       </c>
       <c r="B41" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C41">
         <v>8</v>
@@ -8481,10 +8495,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B42" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C42">
         <v>8</v>
@@ -8492,10 +8506,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B43" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C43">
         <v>8</v>
@@ -8506,7 +8520,7 @@
         <v>254</v>
       </c>
       <c r="B44" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C44">
         <v>8</v>
@@ -8514,10 +8528,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B45" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C45">
         <v>8</v>
@@ -8525,10 +8539,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B46" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C46">
         <v>8</v>
@@ -8536,10 +8550,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B47" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C47">
         <v>8</v>
@@ -8547,10 +8561,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B48" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -8558,10 +8572,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B49" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -8569,10 +8583,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C50">
         <v>7</v>
@@ -8580,10 +8594,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B51" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -8591,10 +8605,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B52" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -8602,10 +8616,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B53" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -8613,10 +8627,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B54" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -8627,7 +8641,7 @@
         <v>164</v>
       </c>
       <c r="B55" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -8635,10 +8649,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B56" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -8649,7 +8663,7 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -8657,10 +8671,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B58" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -8671,7 +8685,7 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -8679,10 +8693,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B60" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C60">
         <v>7</v>
@@ -8690,10 +8704,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B61" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -8701,10 +8715,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -8712,10 +8726,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B63" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -8723,10 +8737,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B64" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -8734,10 +8748,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B65" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -8748,7 +8762,7 @@
         <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -8756,10 +8770,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C67">
         <v>7</v>
@@ -8767,10 +8781,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B68" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -8778,10 +8792,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B69" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C69">
         <v>7</v>
@@ -8792,7 +8806,7 @@
         <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C70">
         <v>7</v>
@@ -8800,10 +8814,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B71" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -8811,10 +8825,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B72" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C72">
         <v>7</v>
@@ -8822,10 +8836,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B73" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C73">
         <v>7</v>
@@ -8833,10 +8847,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B74" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C74">
         <v>7</v>
@@ -8844,10 +8858,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B75" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -8858,7 +8872,7 @@
         <v>65</v>
       </c>
       <c r="B76" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C76">
         <v>6</v>
@@ -8869,7 +8883,7 @@
         <v>103</v>
       </c>
       <c r="B77" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C77">
         <v>6</v>
@@ -8877,10 +8891,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B78" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C78">
         <v>6</v>
@@ -8891,7 +8905,7 @@
         <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C79">
         <v>6</v>
@@ -8899,10 +8913,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B80" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C80">
         <v>6</v>
@@ -8910,10 +8924,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B81" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C81">
         <v>6</v>
@@ -8921,10 +8935,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B82" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C82">
         <v>6</v>
@@ -8932,10 +8946,10 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B83" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C83">
         <v>6</v>
@@ -8943,10 +8957,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B84" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C84">
         <v>6</v>
@@ -8954,10 +8968,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B85" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C85">
         <v>6</v>
@@ -8968,7 +8982,7 @@
         <v>147</v>
       </c>
       <c r="B86" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C86">
         <v>6</v>
@@ -8976,10 +8990,10 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B87" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C87">
         <v>6</v>
@@ -8987,10 +9001,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>662</v>
+      </c>
+      <c r="B88" t="s">
         <v>663</v>
-      </c>
-      <c r="B88" t="s">
-        <v>664</v>
       </c>
       <c r="C88">
         <v>6</v>
@@ -8998,10 +9012,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B89" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C89">
         <v>6</v>
@@ -9009,10 +9023,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B90" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C90">
         <v>6</v>
@@ -9020,10 +9034,10 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B91" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C91">
         <v>6</v>
@@ -9031,10 +9045,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B92" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C92">
         <v>6</v>
@@ -9042,10 +9056,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
+        <v>668</v>
+      </c>
+      <c r="B93" t="s">
         <v>669</v>
-      </c>
-      <c r="B93" t="s">
-        <v>670</v>
       </c>
       <c r="C93">
         <v>6</v>
@@ -9053,10 +9067,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B94" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C94">
         <v>6</v>
@@ -9064,10 +9078,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B95" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C95">
         <v>6</v>
@@ -9078,7 +9092,7 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C96">
         <v>6</v>
@@ -9086,10 +9100,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B97" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C97">
         <v>6</v>
@@ -9100,7 +9114,7 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C98">
         <v>6</v>
@@ -9111,7 +9125,7 @@
         <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C99">
         <v>6</v>
@@ -9119,10 +9133,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B100" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C100">
         <v>6</v>
@@ -9130,10 +9144,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B101" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C101">
         <v>6</v>
@@ -9144,7 +9158,7 @@
         <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C102">
         <v>6</v>
@@ -9152,10 +9166,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B103" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -9166,7 +9180,7 @@
         <v>150</v>
       </c>
       <c r="B104" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C104">
         <v>6</v>
@@ -9174,10 +9188,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B105" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -9185,10 +9199,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B106" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -9196,10 +9210,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B107" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -9207,10 +9221,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B108" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C108">
         <v>6</v>
@@ -9218,10 +9232,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C109">
         <v>6</v>
@@ -9229,10 +9243,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B110" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C110">
         <v>6</v>
@@ -9240,10 +9254,10 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B111" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C111">
         <v>6</v>
@@ -9251,10 +9265,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B112" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C112">
         <v>6</v>
@@ -9262,10 +9276,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B113" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C113">
         <v>6</v>
@@ -9273,10 +9287,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B114" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C114">
         <v>6</v>
@@ -9287,7 +9301,7 @@
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C115">
         <v>6</v>
@@ -9295,10 +9309,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B116" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C116">
         <v>6</v>
@@ -9306,10 +9320,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B117" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C117">
         <v>6</v>
@@ -9317,10 +9331,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
+        <v>686</v>
+      </c>
+      <c r="B118" t="s">
         <v>687</v>
-      </c>
-      <c r="B118" t="s">
-        <v>688</v>
       </c>
       <c r="C118">
         <v>6</v>
@@ -9331,7 +9345,7 @@
         <v>253</v>
       </c>
       <c r="B119" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C119">
         <v>6</v>
@@ -9339,10 +9353,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B120" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C120">
         <v>6</v>
@@ -9353,7 +9367,7 @@
         <v>36</v>
       </c>
       <c r="B121" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C121">
         <v>6</v>
@@ -9364,7 +9378,7 @@
         <v>160</v>
       </c>
       <c r="B122" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C122">
         <v>6</v>
@@ -9375,7 +9389,7 @@
         <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C123">
         <v>6</v>
@@ -9383,10 +9397,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B124" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C124">
         <v>6</v>
@@ -9397,7 +9411,7 @@
         <v>51</v>
       </c>
       <c r="B125" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C125">
         <v>6</v>
@@ -9405,10 +9419,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B126" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C126">
         <v>5</v>
@@ -9416,10 +9430,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B127" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -9427,10 +9441,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B128" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C128">
         <v>5</v>
@@ -9438,10 +9452,10 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B129" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C129">
         <v>5</v>
@@ -9449,10 +9463,10 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B130" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C130">
         <v>5</v>
@@ -9460,10 +9474,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B131" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C131">
         <v>5</v>
@@ -9471,10 +9485,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B132" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C132">
         <v>5</v>
@@ -9482,10 +9496,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B133" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -9493,10 +9507,10 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B134" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C134">
         <v>5</v>
@@ -9504,10 +9518,10 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B135" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C135">
         <v>5</v>
@@ -9515,10 +9529,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B136" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C136">
         <v>5</v>
@@ -9526,10 +9540,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B137" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C137">
         <v>5</v>
@@ -9537,10 +9551,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B138" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C138">
         <v>5</v>
@@ -9548,10 +9562,10 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B139" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C139">
         <v>5</v>
@@ -9559,10 +9573,10 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B140" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C140">
         <v>5</v>
@@ -9570,10 +9584,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B141" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C141">
         <v>5</v>
@@ -9584,7 +9598,7 @@
         <v>70</v>
       </c>
       <c r="B142" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C142">
         <v>5</v>
@@ -9595,7 +9609,7 @@
         <v>5</v>
       </c>
       <c r="B143" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C143">
         <v>5</v>
@@ -9603,10 +9617,10 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B144" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C144">
         <v>5</v>
@@ -9614,10 +9628,10 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B145" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C145">
         <v>5</v>
@@ -9625,10 +9639,10 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B146" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C146">
         <v>5</v>
@@ -9639,7 +9653,7 @@
         <v>44</v>
       </c>
       <c r="B147" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C147">
         <v>5</v>
@@ -9647,10 +9661,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B148" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C148">
         <v>5</v>
@@ -9658,10 +9672,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B149" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C149">
         <v>5</v>
@@ -9669,10 +9683,10 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B150" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C150">
         <v>5</v>
@@ -9680,10 +9694,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B151" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C151">
         <v>5</v>
@@ -9691,10 +9705,10 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B152" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C152">
         <v>5</v>
@@ -9702,10 +9716,10 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B153" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C153">
         <v>5</v>
@@ -9713,10 +9727,10 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B154" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C154">
         <v>5</v>
@@ -9724,10 +9738,10 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B155" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C155">
         <v>5</v>
@@ -9735,10 +9749,10 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B156" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C156">
         <v>5</v>
@@ -9746,10 +9760,10 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B157" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -9760,7 +9774,7 @@
         <v>250</v>
       </c>
       <c r="B158" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C158">
         <v>5</v>
@@ -9768,10 +9782,10 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B159" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C159">
         <v>5</v>
@@ -9779,10 +9793,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B160" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C160">
         <v>5</v>
@@ -9793,7 +9807,7 @@
         <v>87</v>
       </c>
       <c r="B161" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -9801,10 +9815,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B162" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -9812,10 +9826,10 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B163" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C163">
         <v>5</v>
@@ -9823,10 +9837,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B164" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C164">
         <v>5</v>
@@ -9834,10 +9848,10 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B165" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C165">
         <v>5</v>
@@ -9848,7 +9862,7 @@
         <v>97</v>
       </c>
       <c r="B166" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C166">
         <v>5</v>
@@ -9856,10 +9870,10 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B167" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -9867,10 +9881,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B168" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C168">
         <v>5</v>
@@ -9878,10 +9892,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
+        <v>724</v>
+      </c>
+      <c r="B169" t="s">
         <v>725</v>
-      </c>
-      <c r="B169" t="s">
-        <v>726</v>
       </c>
       <c r="C169">
         <v>5</v>
@@ -9889,10 +9903,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B170" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C170">
         <v>5</v>
@@ -9900,10 +9914,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
+        <v>727</v>
+      </c>
+      <c r="B171" t="s">
         <v>728</v>
-      </c>
-      <c r="B171" t="s">
-        <v>729</v>
       </c>
       <c r="C171">
         <v>5</v>
@@ -9911,10 +9925,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B172" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C172">
         <v>5</v>
@@ -9922,10 +9936,10 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B173" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C173">
         <v>5</v>
@@ -9933,10 +9947,10 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B174" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -9944,10 +9958,10 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B175" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -9958,7 +9972,7 @@
         <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C176">
         <v>5</v>
@@ -9966,10 +9980,10 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B177" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -9980,7 +9994,7 @@
         <v>116</v>
       </c>
       <c r="B178" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -9988,10 +10002,10 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B179" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -9999,10 +10013,10 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B180" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C180">
         <v>5</v>
@@ -10010,10 +10024,10 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B181" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C181">
         <v>5</v>
@@ -10021,10 +10035,10 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B182" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C182">
         <v>5</v>
@@ -10032,10 +10046,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B183" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C183">
         <v>5</v>
@@ -10043,10 +10057,10 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B184" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C184">
         <v>5</v>
@@ -10054,10 +10068,10 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B185" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C185">
         <v>5</v>
@@ -10065,10 +10079,10 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
+        <v>741</v>
+      </c>
+      <c r="B186" t="s">
         <v>742</v>
-      </c>
-      <c r="B186" t="s">
-        <v>743</v>
       </c>
       <c r="C186">
         <v>5</v>
@@ -10076,10 +10090,10 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B187" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C187">
         <v>5</v>
@@ -10087,10 +10101,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B188" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C188">
         <v>5</v>
@@ -10098,10 +10112,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B189" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C189">
         <v>5</v>
@@ -10109,10 +10123,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B190" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C190">
         <v>5</v>
@@ -10123,7 +10137,7 @@
         <v>91</v>
       </c>
       <c r="B191" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C191">
         <v>5</v>
@@ -10131,10 +10145,10 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B192" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C192">
         <v>5</v>
@@ -10142,10 +10156,10 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B193" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C193">
         <v>5</v>
@@ -10156,7 +10170,7 @@
         <v>14</v>
       </c>
       <c r="B194" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C194">
         <v>5</v>
@@ -10164,10 +10178,10 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
+        <v>749</v>
+      </c>
+      <c r="B195" t="s">
         <v>750</v>
-      </c>
-      <c r="B195" t="s">
-        <v>751</v>
       </c>
       <c r="C195">
         <v>5</v>
@@ -10175,10 +10189,10 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B196" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C196">
         <v>5</v>
@@ -10186,10 +10200,10 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B197" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C197">
         <v>5</v>
@@ -10197,10 +10211,10 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B198" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -10208,10 +10222,10 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B199" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C199">
         <v>5</v>
@@ -10219,10 +10233,10 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B200" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C200">
         <v>5</v>
@@ -10230,10 +10244,10 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B201" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C201">
         <v>5</v>
@@ -10241,10 +10255,10 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B202" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C202">
         <v>5</v>
@@ -10252,10 +10266,10 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B203" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C203">
         <v>5</v>
@@ -10263,10 +10277,10 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B204" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -10274,10 +10288,10 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B205" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -10285,10 +10299,10 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B206" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -10296,10 +10310,10 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B207" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -10307,10 +10321,10 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B208" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -10318,10 +10332,10 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B209" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -10329,10 +10343,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B210" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -10340,10 +10354,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B211" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C211">
         <v>5</v>
@@ -10351,10 +10365,10 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B212" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C212">
         <v>5</v>
@@ -10365,7 +10379,7 @@
         <v>248</v>
       </c>
       <c r="B213" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C213">
         <v>5</v>
@@ -10376,7 +10390,7 @@
         <v>47</v>
       </c>
       <c r="B214" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C214">
         <v>5</v>
@@ -10387,7 +10401,7 @@
         <v>49</v>
       </c>
       <c r="B215" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C215">
         <v>5</v>
@@ -10395,10 +10409,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B216" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C216">
         <v>5</v>
